--- a/AAII_Financials/Quarterly/NVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVS_QTR_FIN.xlsx
@@ -656,521 +656,533 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14951000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13524000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13860000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14358000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14836000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13620000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13558000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13172000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12872000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12120000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11776000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12092000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11745000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11047000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10880000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10783000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21712000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12814000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13522000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13367000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13294000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12694000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13030000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12538000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11622000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12708000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12716000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12482000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12024000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11402000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11876000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>11358000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>11633000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12929000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>13164000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>12692000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>12494000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>11785000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>12556000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>12341000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3678000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3438000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3542000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3535000</v>
       </c>
-      <c r="G9" s="3">
-        <v>3319000</v>
-      </c>
       <c r="H9" s="3">
+        <v>3322000</v>
+      </c>
+      <c r="I9" s="3">
         <v>3227000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3312000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3234000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3173000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3096000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2570000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3117000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3342000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2991000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6878000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6531000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9416000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3755000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4000000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3848000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3754000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3833000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3940000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3568000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3337000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3555000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3834000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3616000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3315000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3165000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8368000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7646000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7874000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4257000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4393000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4292000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4210000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4063000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4426000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>4309000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11273000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10086000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10318000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10823000</v>
       </c>
-      <c r="G10" s="3">
-        <v>11517000</v>
-      </c>
       <c r="H10" s="3">
+        <v>11514000</v>
+      </c>
+      <c r="I10" s="3">
         <v>10393000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10246000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9938000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9699000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9024000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9206000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8975000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8403000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8056000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4002000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4252000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12296000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9059000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9522000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9519000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9540000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8861000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9090000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8970000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8285000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9153000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8882000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8866000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8709000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8237000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3508000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3712000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3759000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8672000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8771000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8400000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8284000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>7722000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>8130000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>8032000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1213,130 +1225,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2739000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2785000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2837000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2864000</v>
       </c>
-      <c r="G12" s="3">
-        <v>2616000</v>
-      </c>
       <c r="H12" s="3">
+        <v>2727000</v>
+      </c>
+      <c r="I12" s="3">
         <v>2366000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2331000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2392000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2367000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2421000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>207000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3925000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2304000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2575000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4507000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4805000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6665000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2256000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2369000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2261000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2284000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2127000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2297000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2143000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2010000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2034000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2193000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2175000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2054000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1964000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>4553000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>4217000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>4307000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>2111000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2251000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>2049000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>2029000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1984000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>2173000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>2080000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1457,192 +1473,198 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>462000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-59000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>274000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>97000</v>
       </c>
-      <c r="G14" s="3">
-        <v>628000</v>
-      </c>
       <c r="H14" s="3">
+        <v>147000</v>
+      </c>
+      <c r="I14" s="3">
         <v>41000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2007000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-29000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>16000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3673000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-96000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>106000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-535000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1406000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1112000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>993000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>295000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>305000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>271000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-136000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>690000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>66000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1067000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>731000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>302000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>784000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>505000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>456000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>453000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1116000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>744000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-5483000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>181000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>170000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>166000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>68000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>220000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-152000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>160000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1116000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1101000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1190000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1092000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1085000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1094000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1055000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1093000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1084000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1252000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1194000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1314000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>42000</v>
       </c>
       <c r="R15" s="3">
         <v>42000</v>
       </c>
       <c r="S15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="T15" s="3">
         <v>39000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>35000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>30000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>25000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>27000</v>
       </c>
       <c r="X15" s="3">
         <v>27000</v>
@@ -1651,58 +1673,61 @@
         <v>27000</v>
       </c>
       <c r="Z15" s="3">
+        <v>27000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>12000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>11000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>14000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>15000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>13000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>10000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>12000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>15000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>145000</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>15000</v>
       </c>
       <c r="AJ15" s="3">
         <v>15000</v>
       </c>
       <c r="AK15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="AL15" s="3">
         <v>140000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>16000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>24000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>17000</v>
-      </c>
-      <c r="AO15" s="3">
-        <v>13000</v>
       </c>
       <c r="AP15" s="3">
         <v>13000</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>13000</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1742,252 +1767,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>9775000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9402000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10005000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9773000</v>
       </c>
-      <c r="G17" s="3">
-        <v>9372000</v>
-      </c>
       <c r="H17" s="3">
+        <v>9825000</v>
+      </c>
+      <c r="I17" s="3">
         <v>8916000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8252000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9538000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8887000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8731000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5715000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10426000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8832000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8964000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9125000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8957000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17347000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9962000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10960000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10134000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9815000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10279000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10386000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10126000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9270000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9964000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10893000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10124000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9361000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9160000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10515000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9119000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3411000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10482000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11094000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>10335000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>10214000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>9863000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>11101000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>10072000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>5176000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4122000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3855000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4585000</v>
       </c>
-      <c r="G18" s="3">
-        <v>5464000</v>
-      </c>
       <c r="H18" s="3">
+        <v>5011000</v>
+      </c>
+      <c r="I18" s="3">
         <v>4704000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5306000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3634000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3985000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3389000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6061000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1666000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2913000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2083000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1755000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1826000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4365000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2852000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2562000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3233000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3479000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2415000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2644000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2412000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2352000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2744000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1823000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2358000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2663000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2242000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1361000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2239000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8222000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2447000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2070000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2357000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2280000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1922000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1455000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2269000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2030,618 +2062,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>432000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>11000</v>
       </c>
-      <c r="G20" s="3">
-        <v>16000</v>
-      </c>
       <c r="H20" s="3">
+        <v>44000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-14000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>307000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-22000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-73000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>23000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>421000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-83000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-102000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>21000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-33000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>43000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>18000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>14595000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>199000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>228000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>237000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>116000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>207000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>156000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>116000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>139000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>265000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>176000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>124000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>220000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>241000</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>186000</v>
       </c>
       <c r="AJ20" s="3">
         <v>186000</v>
       </c>
       <c r="AK20" s="3">
+        <v>186000</v>
+      </c>
+      <c r="AL20" s="3">
         <v>439000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>276000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>227000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>205000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-209000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>179000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>6316000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5239000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4524000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5764000</v>
       </c>
-      <c r="G21" s="3">
-        <v>6540000</v>
-      </c>
       <c r="H21" s="3">
+        <v>6059000</v>
+      </c>
+      <c r="I21" s="3">
         <v>5803000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6099000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4750000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5113000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4459000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6724000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2930000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4190000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3499000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3724000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3819000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7615000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4275000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>18676000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4885000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5151000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4349000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4377000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4353000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4211000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4270000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3899000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4025000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3885000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3807000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3217000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3845000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>9688000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3887000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3977000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>4111000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3861000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3903000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2946000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3956000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>462000</v>
+      </c>
+      <c r="E22" s="3">
         <v>343000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>304000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>281000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>289000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>270000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>275000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>264000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>246000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>221000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>217000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>222000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>216000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>200000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>207000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>206000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>387000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>201000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>206000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>202000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>201000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>202000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>201000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>209000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>220000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>239000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>203000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>216000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>205000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>226000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>248000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>229000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>237000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>224000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>208000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>197000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>192000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>180000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>168000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>174000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>4269000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3839000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3218000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4196000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4531000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4407000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3285000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3385000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3841000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3129000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2377000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1552000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2674000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2520000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1569000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1587000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4021000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2669000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>16951000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3230000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3506000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2450000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2559000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2410000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2288000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2621000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1759000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2407000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2634000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2140000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1333000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2251000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>8171000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2409000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2301000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2436000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2315000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1947000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1078000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2274000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1012000</v>
+      </c>
+      <c r="E24" s="3">
         <v>683000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>814000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>266000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>507000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>798000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>465000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>595000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>441000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-261000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>39000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>403000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>370000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>254000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>257000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>617000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>450000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>645000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>472000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>611000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>391000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>460000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>478000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>421000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>448000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>630000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>366000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>525000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>272000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>113000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>369000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>443000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>381000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>386000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>353000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>336000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>282000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>142000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>329000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2762,252 +2810,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3257000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3156000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2404000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3930000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4024000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3609000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2820000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3185000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3246000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2688000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2638000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1513000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2271000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2150000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1315000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1330000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3404000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2219000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16306000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2758000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2895000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2059000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2099000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1932000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1867000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2173000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1129000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2041000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2109000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1868000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1220000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1882000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>7728000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2028000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1915000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2083000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1979000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1665000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>936000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1945000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3156000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2409000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3928000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4041000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3606000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2818000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3189000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3246000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2688000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8480000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1761000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2316000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2293000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1315000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1328000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3406000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2222000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16308000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2758000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2896000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2059000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2094000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1935000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1867000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2176000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1125000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2042000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2108000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1867000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1221000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1881000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7728000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2025000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1915000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2081000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1980000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1666000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>957000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1940000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3128,8 +3185,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3161,32 +3221,32 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>5842000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>250000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>46000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>144000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>151000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>245000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>510000</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -3196,8 +3256,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>24</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>24</v>
@@ -3208,35 +3268,35 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>4691000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-101000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-258000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>40000</v>
       </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>61000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3250,8 +3310,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3372,8 +3435,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3494,252 +3560,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-432000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-11000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-16000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="I32" s="3">
         <v>14000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-307000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>22000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>73000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-23000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-421000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>83000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>102000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-21000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>33000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-43000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-18000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-14595000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-199000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-228000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-237000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-116000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-207000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-156000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-116000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-139000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-265000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-176000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-124000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-220000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-241000</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-186000</v>
       </c>
       <c r="AJ32" s="3">
         <v>-186000</v>
       </c>
       <c r="AK32" s="3">
+        <v>-186000</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-439000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-227000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-205000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>209000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-179000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3156000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2409000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3928000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4041000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3606000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2818000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3189000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3246000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2688000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8480000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1761000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2316000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2293000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1466000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1573000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3916000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2222000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16308000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2758000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2896000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2059000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2094000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1935000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1867000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2176000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1125000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2042000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6799000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1766000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1195000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1623000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7768000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2025000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1976000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2081000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1980000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1666000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>957000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1940000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3860,257 +3935,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3156000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2409000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3928000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4041000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3606000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2818000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3189000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3246000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2688000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8480000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1761000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2316000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2293000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1466000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1573000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3916000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2222000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16308000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2758000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2896000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2059000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2094000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1935000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1867000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2176000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1125000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2042000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6799000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1766000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1195000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1623000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7768000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2025000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1976000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2081000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1980000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1666000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>957000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1940000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4153,8 +4237,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4197,234 +4282,238 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7616000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6877000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11435000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9556000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6656000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7066000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11459000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13609000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7903000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9469000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13393000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12405000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10885000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12000000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7517000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8726000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3625000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13852000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12407000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7211000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5117000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3801000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9658000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8994000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5917000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4528000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11112000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8378000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9991000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6807000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13271000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14000000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>12446000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5813000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>9485000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>9421000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>8437000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>8237000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>7007000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>7785000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E42" s="3">
         <v>15000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>98000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>112000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>76000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>71000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1892000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>242000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>528000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>234000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>680000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>411000</v>
-      </c>
-      <c r="O42" s="3">
-        <v>187000</v>
       </c>
       <c r="P42" s="3">
         <v>187000</v>
       </c>
       <c r="Q42" s="3">
+        <v>187000</v>
+      </c>
+      <c r="R42" s="3">
         <v>11209000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>10377000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>16133000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>4962000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>15922000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>951000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>239000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>276000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1905000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1876000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>376000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>445000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>334000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>339000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>344000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>305000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2693000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>710000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>700000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>609000</v>
-      </c>
-      <c r="AK42" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AL42" s="3" t="s">
         <v>24</v>
@@ -4435,868 +4524,892 @@
       <c r="AN42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AO42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP42" s="3">
         <v>770000</v>
       </c>
-      <c r="AP42" s="3" t="s">
+      <c r="AQ42" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9854000</v>
+      </c>
+      <c r="E43" s="3">
         <v>9602000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10833000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8984000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9176000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8725000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9131000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8150000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8480000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8251000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9247000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7099000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9543000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9183000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9894000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8680000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8910000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8678000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8283000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8632000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8654000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8481000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8456000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8299000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7952000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8795000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8555000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8070000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8252000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7845000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8975000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8766000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8989000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9116000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8802000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>8482000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>8380000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>8234000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8202000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>8547000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6220000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6286000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6269000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6421000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6307000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5829000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5723000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5939000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5747000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5743000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5913000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5610000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8228000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7886000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7175000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6779000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6880000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6997000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6666000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6885000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7111000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6997000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7131000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7136000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6904000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6398000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5982000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6123000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6094000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5728000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>6956000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>6952000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>7097000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>7227000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>6867000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>6954000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>6901000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>6583000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>6255000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>6773000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3659000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3827000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>672000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3125000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3724000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3417000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>514000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3324000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3035000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2750000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>484000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>20135000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4650000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2858000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1115000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2392000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2594000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2747000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2440000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2574000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2687000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2643000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2523000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2668000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2733000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2932000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3521000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3765000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3639000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>31763000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3668000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3685000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2833000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>10286000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3054000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2609000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2820000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2712000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2697000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>2778000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27351000</v>
+      </c>
+      <c r="E46" s="3">
         <v>26607000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>30460000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28198000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25939000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25108000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29704000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>31264000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25693000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>26447000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>30481000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>45660000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>33493000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32114000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>36910000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36954000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>38142000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>37236000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>45718000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>26253000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>23808000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>22198000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>29673000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>28973000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>23882000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>23098000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>29504000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>26675000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>28320000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>52448000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>35563000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>34113000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>32065000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>33051000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>28208000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>27466000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>26538000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>25766000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>24931000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>25883000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>371000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1656000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1091000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1407000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1400000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1409000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1128000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1545000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1625000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2102000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1827000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1530000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1758000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1788000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2554000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2491000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2580000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2906000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3241000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12347000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12014000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>11628000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12533000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>11603000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>11050000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>10521000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>11162000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>11062000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>11638000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10122000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>10697000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>10807000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>10359000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>10521000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>26660000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>28692000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>27926000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>27722000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>16500000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>27723000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12267000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12238000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12352000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11991000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11826000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11087000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10873000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11201000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10622000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10542000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10924000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10344000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12277000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12348000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12195000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11731000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12206000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12861000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13106000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13157000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13344000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13204000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13939000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13337000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13595000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13560000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13746000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13560000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14052000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14136000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15696000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>15745000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>15957000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>16677000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>16464000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>16263000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>16206000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>15772000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>15641000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>16199000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>68841000</v>
+      </c>
+      <c r="E49" s="3">
         <v>67028000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>54978000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>54588000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>54793000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>52441000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>51671000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>52832000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>53009000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>49335000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>50220000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>49834000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>57525000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>59932000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>60945000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>60556000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>62480000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>64489000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>63777000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>63523000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>64584000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>64967000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>66808000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>66415000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>65769000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>66388000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>55311000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>56000000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>53754000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>53316000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>74013000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>72989000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>74610000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>66250000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>61747000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>62551000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>63079000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>62726000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>62320000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>64202000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5417,8 +5530,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5539,112 +5655,115 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7926000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5756000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6436000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5529000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5235000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4797000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4355000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2036000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2156000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1689000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1966000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1701000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1883000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1978000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4849000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6732000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7502000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7726000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5953000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5929000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10265000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9755000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4825000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9350000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9467000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9530000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8647000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8674000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8530000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7924000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9594000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9340000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9067000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9025000</v>
-      </c>
-      <c r="AK52" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AL52" s="3" t="s">
         <v>24</v>
@@ -5655,14 +5774,17 @@
       <c r="AN52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AO52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP52" s="3">
         <v>10732000</v>
       </c>
-      <c r="AP52" s="3" t="s">
+      <c r="AQ52" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5783,130 +5905,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>122033000</v>
+      </c>
+      <c r="E54" s="3">
         <v>118532000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>110949000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>107289000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>104395000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>99941000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>102246000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>103524000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97505000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94334000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>99945000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>112697000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>110979000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>112241000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>117453000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>118464000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>122910000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>125218000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>131795000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>121209000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>124015000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>121752000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>127778000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>129678000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>123763000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>123097000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>118370000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>115971000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>116294000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>137946000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>145563000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>142994000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>142058000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>135524000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>133079000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>134972000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>133749000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>131986000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>130124000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>134007000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5949,8 +6077,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5993,740 +6122,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4258000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4322000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4456000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4555000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4506000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4261000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4572000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4087000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4146000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4062000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4926000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3870000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5350000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5426000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5146000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4693000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4969000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5083000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5553000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4665000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4811000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5040000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5403000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4705000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4820000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4828000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5424000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4669000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4752000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4638000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5556000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4970000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5486000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4994000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>5169000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4685000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4691000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4566000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4873000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>4662000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9862000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7888000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5865000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7784000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8573000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8043000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8467000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6813000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7764000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8564000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6405000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5668000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8536000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7219000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6127000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7204000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7247000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6902000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6502000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9528000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9278000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>10400000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10071000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>9994000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>9133000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11205000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7277000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8283000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8151000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7701000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>9678000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>9177000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>9596000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>10911000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>5308000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>6997000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>7562000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>8324000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>5905000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>8307000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17628000</v>
+      </c>
+      <c r="E59" s="3">
         <v>19164000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11595000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19661000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18635000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19315000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10665000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17232000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15702000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16662000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9885000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38855000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18023000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17904000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17383000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16263000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15430000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17822000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18153000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15687000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15544000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14720000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17585000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17139000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15429000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15261000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15563000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15268000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17208000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>43788000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14373000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>14180000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>12861000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>12318000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>12926000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>13697000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>13893000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>13440000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>11431000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>11635000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31748000</v>
+      </c>
+      <c r="E60" s="3">
         <v>31374000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27278000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32000000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31714000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>31619000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28692000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28132000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27612000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29288000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26390000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>48393000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31909000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30549000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28656000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>28160000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27646000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29807000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>30208000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>29880000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>29633000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>30160000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>33059000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>31838000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>29382000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>31294000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>28264000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>28220000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>30111000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>56127000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>29607000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>28327000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>27943000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>28223000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>23403000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>25379000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>26146000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>26330000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>22209000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>24604000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39152000</v>
+      </c>
+      <c r="E61" s="3">
         <v>39110000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29592000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24238000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24064000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23227000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22934000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25346000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21223000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18720000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20034000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19521000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19804000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21985000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21782000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21235000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23784000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24373000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24523000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>24715000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26491000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>27399000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>27978000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28181000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>25653000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>25490000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>22056000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>21833000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>22116000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>22889000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>22470000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>22605000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>22760000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>23199000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>23224000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>23163000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>22999000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>22933000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>17897000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>18259000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3895000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4017000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1569000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4128000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4242000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4095000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1602000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4389000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4312000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4259000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1793000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4081000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4809000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4838000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7592000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8171000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8474000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9334000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9242000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9677000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13763000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13604000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>17009000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>15105000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>14843000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>15336000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>12499000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13320000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>12563000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11623000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>14794000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>14043000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>14454000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>12891000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>12225000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>14060000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>14626000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>15077000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>15127000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>16078000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6847,8 +6995,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6969,8 +7120,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7091,130 +7245,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>80087000</v>
+      </c>
+      <c r="E66" s="3">
         <v>79605000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>64400000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>62537000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>62341000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>61489000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>58120000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>60083000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55603000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54578000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53195000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74452000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>59048000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60099000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>58111000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>57644000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59985000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>63678000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>64140000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>64438000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>69973000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>71229000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>71180000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>75194000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>69951000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>72194000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>62896000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>63447000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>64868000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>90717000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>66949000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>65056000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>65243000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>64426000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>58911000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>62661000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>63830000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>64400000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>55292000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>59023000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7257,8 +7417,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7379,8 +7540,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7501,8 +7665,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7623,8 +7790,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7745,112 +7915,115 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>39649000</v>
+      </c>
+      <c r="E72" s="3">
         <v>37252000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44720000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>43510000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>41527000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>39839000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>46561000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>46292000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>45836000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>43834000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49649000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>42333000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>55682000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>56089000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>63540000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>60000000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>62095000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>60699000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>66802000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>55917000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>53194000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>49670000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>55738000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>53615000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>52936000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>50035000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>54618000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>51668000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>50557000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>46348000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>77739000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>77063000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>75934000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>70222000</v>
-      </c>
-      <c r="AK72" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AL72" s="3" t="s">
         <v>24</v>
@@ -7867,8 +8040,11 @@
       <c r="AP72" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ72" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7989,8 +8165,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8111,8 +8290,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8233,130 +8415,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41542000</v>
+      </c>
+      <c r="E76" s="3">
         <v>38512000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>46130000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44330000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>41985000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>38369000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44046000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43317000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41733000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>39675000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46667000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38164000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>51847000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52059000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>59342000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>60820000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>62925000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>61540000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>67655000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>56771000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>54042000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>50523000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>56598000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>54484000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>53812000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>50903000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>55474000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>52524000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>51426000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>47229000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>78614000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>77938000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>76815000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>71098000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>74168000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>72311000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>69919000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>67586000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>74832000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>74984000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8477,257 +8665,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3156000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2409000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3928000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4041000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3606000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2818000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3189000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3246000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2688000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8480000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1761000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2316000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2293000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1466000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1573000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3916000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2222000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16308000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2758000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2896000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2059000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2094000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1935000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1867000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2176000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1125000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2042000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6799000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1766000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1195000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1623000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7768000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2025000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1976000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2081000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1980000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1666000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>957000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1940000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8770,130 +8967,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>309000</v>
+      </c>
+      <c r="E83" s="3">
         <v>280000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>293000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>288000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>280000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>281000</v>
       </c>
-      <c r="I83" s="3">
-        <v>-1518000</v>
-      </c>
       <c r="J83" s="3">
+        <v>254000</v>
+      </c>
+      <c r="K83" s="3">
         <v>302000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>289000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>299000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>319000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>312000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>371000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1948000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2026000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3207000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1405000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1519000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1453000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1444000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1697000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1617000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1734000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1703000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1410000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1937000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1402000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1046000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1441000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>3199000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2963000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2893000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1254000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1468000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1478000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1354000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1776000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1700000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1508000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9014,8 +9215,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9136,8 +9340,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9258,8 +9465,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9380,8 +9590,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9502,130 +9715,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5882000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3676000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2264000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6571000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6664000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3645000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4193000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6286000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4875000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2265000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2547000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5378000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3576000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2957000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4111000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4721000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5404000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1649000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3884000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4925000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4132000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2130000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4005000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3156000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3961000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2528000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3540000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4562000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3610000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1913000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3766000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4050000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3942000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2514000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3408000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3586000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3582000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2045000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3231000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9668,130 +9887,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-321000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-346000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-609000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-354000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-331000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-254000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-558000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-321000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-260000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-227000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-406000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-261000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-225000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-168000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-647000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-582000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-583000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-859000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-977000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-539000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-321000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-246000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-521000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-279000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-238000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-237000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-461000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-357000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-279000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-282000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-444000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-295000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-257000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-359000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-638000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-382000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-332000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-554000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-516000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-979000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9912,8 +10135,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10034,130 +10260,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3105000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11736000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2104000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-860000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2243000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>330000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3033000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-374000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3207000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-899000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1760000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2212000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1053000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>10621000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1467000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>5198000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2263000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>9365000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>4563000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1232000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>97000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>780000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-571000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-425000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-10141000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>318000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3398000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-474000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1328000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4935000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-886000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>4325000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4095000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-996000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-685000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-337000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1101000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1073000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-752000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10200,64 +10432,65 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2871000</v>
+      </c>
+      <c r="E96" s="3">
         <v>6197000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2485000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>5333000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="s">
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2417000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>5207000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>24</v>
+      <c r="N96" s="3">
+        <v>0</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q96" s="3">
         <v>7255000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
-        <v>-7506000</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-7506000</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-7506000</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
@@ -10266,11 +10499,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-7368000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -10278,11 +10511,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-6987000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -10290,11 +10523,11 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-6645000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
@@ -10302,11 +10535,11 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-6966000</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
@@ -10314,16 +10547,19 @@
         <v>0</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-6495000</v>
       </c>
-      <c r="AO96" s="3">
-        <v>0</v>
-      </c>
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10444,8 +10680,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10566,8 +10805,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10688,370 +10930,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2020000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3579000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1683000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2789000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5213000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8548000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2996000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-382000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3200000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5164000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-607000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-832000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3637000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9202000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3994000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4738000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11830000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-9528000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3251000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1534000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2939000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8540000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2936000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1900000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2185000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1013000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2713000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-28000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-9683000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>453000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1621000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1530000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1546000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2396000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1937000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-3012000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-388000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2303000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-342000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E101" s="3">
         <v>180000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-314000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>176000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-34000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-126000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>160000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-166000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>107000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>141000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-80000</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>141000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-80000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-93000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-41000</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-65000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>26000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-227000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>166000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>66000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>38000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>16000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>79000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>76000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>11000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>80000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>34000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>51000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>9000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-382000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>739000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4558000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1879000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2900000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-410000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4393000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2150000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5706000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1566000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3924000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>340000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2168000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1115000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4483000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1209000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5101000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8782000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1445000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5196000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2094000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1316000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5857000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>664000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3077000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1389000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6584000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2734000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1613000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3184000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-6464000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-729000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1554000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6633000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3047000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>50000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>954000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>284000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>565000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>2138000</v>
       </c>
     </row>
